--- a/Open Cart Manual Testing Project/OpenCart_RTM.xlsx
+++ b/Open Cart Manual Testing Project/OpenCart_RTM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarvadnya\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Manual Testing Projects\Open Cart Manual Testing Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,9 +24,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="397">
   <si>
-    <t>Requirements Traceability Matrix (RTM) — OpenCart (Frontend)  |  https://demo.opencart.com  |  By: Rushikesh Bhadange</t>
-  </si>
-  <si>
     <t>Req ID</t>
   </si>
   <si>
@@ -45,9 +42,6 @@
     <t>Defect ID</t>
   </si>
   <si>
-    <t>TS_001</t>
-  </si>
-  <si>
     <t>Validate the working of Register Account functionality</t>
   </si>
   <si>
@@ -180,9 +174,6 @@
     <t>TC_RF_018</t>
   </si>
   <si>
-    <t>Validate whether the fields in the Register Account page are according the Client requirements (Examples- Height, Width, Number of characters etc.)</t>
-  </si>
-  <si>
     <t>TC_RF_019</t>
   </si>
   <si>
@@ -207,9 +198,6 @@
     <t>TC_RF_022</t>
   </si>
   <si>
-    <t>Validate the Password text entered into the 'Password' and 'Password Confirm' field of 'Register Account' functionality is toggled to hide its visibility</t>
-  </si>
-  <si>
     <t>TC_RF_023</t>
   </si>
   <si>
@@ -237,12 +225,6 @@
     <t>TC_RF_027</t>
   </si>
   <si>
-    <t>Validate 'Register Account' functionality in all the supported environments</t>
-  </si>
-  <si>
-    <t>TS_002</t>
-  </si>
-  <si>
     <t>Validate the working of Login functionality</t>
   </si>
   <si>
@@ -330,9 +312,6 @@
     <t>TC_LF_013</t>
   </si>
   <si>
-    <t>Validate the text into the Password field is toggled to hide its visibility</t>
-  </si>
-  <si>
     <t>TC_LF_014</t>
   </si>
   <si>
@@ -396,12 +375,6 @@
     <t>TC_LF_023</t>
   </si>
   <si>
-    <t>Validate the Login page functionality in all the supported environments</t>
-  </si>
-  <si>
-    <t>TS_003</t>
-  </si>
-  <si>
     <t>Validate the working of Logout functionality</t>
   </si>
   <si>
@@ -471,12 +444,6 @@
     <t>TC_LG_011</t>
   </si>
   <si>
-    <t>Validate the Logout functionality in all the supported environments</t>
-  </si>
-  <si>
-    <t>TS_004</t>
-  </si>
-  <si>
     <t>Validate the working of Forgot Password functionality</t>
   </si>
   <si>
@@ -624,18 +591,9 @@
     <t>TC_FP_024</t>
   </si>
   <si>
-    <t>Validate the Password entered into the 'Password' and 'Confirm' fields of 'Reset your Password' page is toggled to hide its visibility</t>
-  </si>
-  <si>
     <t>TC_FP_025</t>
   </si>
   <si>
-    <t>Validate the Password Reset functionality in all the supported environments</t>
-  </si>
-  <si>
-    <t>TS_005</t>
-  </si>
-  <si>
     <t>Validate the working of Search functionality</t>
   </si>
   <si>
@@ -666,9 +624,6 @@
     <t>TC_SF_005</t>
   </si>
   <si>
-    <t>Validate searching by providing a search criteria which results in mulitple products</t>
-  </si>
-  <si>
     <t>TC_SF_006</t>
   </si>
   <si>
@@ -702,33 +657,18 @@
     <t>TC_SF_011</t>
   </si>
   <si>
-    <t>Validate List and Grid views when only one Product is displayed in the search results</t>
-  </si>
-  <si>
     <t>TC_SF_012</t>
   </si>
   <si>
-    <t>Validate List and Grid views when  multiple Products are displayed in the search results</t>
-  </si>
-  <si>
     <t>TC_SF_013</t>
   </si>
   <si>
-    <t>Validate navigating to Product Compare Page from Search Results page</t>
-  </si>
-  <si>
     <t>TC_SF_014</t>
   </si>
   <si>
-    <t>Validate User is able to sort the Products displayed in the Search Results</t>
-  </si>
-  <si>
     <t>TC_SF_015</t>
   </si>
   <si>
-    <t>Validate the User can select how many produts can be displayed in the Search Results</t>
-  </si>
-  <si>
     <t>TC_SF_016</t>
   </si>
   <si>
@@ -771,12 +711,6 @@
     <t>TC_SF_022</t>
   </si>
   <si>
-    <t>Validate the Search functionality in all the supported environments</t>
-  </si>
-  <si>
-    <t>TS_006</t>
-  </si>
-  <si>
     <t>Validate the working of Product Compare functionality</t>
   </si>
   <si>
@@ -789,15 +723,9 @@
     <t>TC_PC_002</t>
   </si>
   <si>
-    <t>Validate adding the product for comparision from List View of Search Results page</t>
-  </si>
-  <si>
     <t>TC_PC_003</t>
   </si>
   <si>
-    <t>Validate adding the product for comparision from Grid View of Search Results page</t>
-  </si>
-  <si>
     <t>TC_PC_004</t>
   </si>
   <si>
@@ -825,9 +753,6 @@
     <t>TC_PC_008</t>
   </si>
   <si>
-    <t>Validate navigating to 'Product Compare' page from Search results page</t>
-  </si>
-  <si>
     <t>TC_PC_009</t>
   </si>
   <si>
@@ -837,9 +762,6 @@
     <t>TC_PC_010</t>
   </si>
   <si>
-    <t>Validate 'Product Compare' page when no products are added for comparison</t>
-  </si>
-  <si>
     <t>TC_PC_011</t>
   </si>
   <si>
@@ -855,9 +777,6 @@
     <t>TC_PC_013</t>
   </si>
   <si>
-    <t>Validate the success message which will be displayed after adding the Products for Comparison</t>
-  </si>
-  <si>
     <t>TC_PC_014</t>
   </si>
   <si>
@@ -867,9 +786,6 @@
     <t>TC_PC_015</t>
   </si>
   <si>
-    <t>Validate the 'Product Comparison' page when only two products are added to the page for comparison</t>
-  </si>
-  <si>
     <t>TC_PC_016</t>
   </si>
   <si>
@@ -879,33 +795,18 @@
     <t>TC_PC_017</t>
   </si>
   <si>
-    <t>Validate the 'Product Comparison' page when three products are added to the page for comparison</t>
-  </si>
-  <si>
     <t>TC_PC_018</t>
   </si>
   <si>
-    <t>Validate the 'Product Comparison' page when four products are added to the page for comparison</t>
-  </si>
-  <si>
     <t>TC_PC_019</t>
   </si>
   <si>
-    <t>Validate that more than 4 products cannot be added to the 'Product Comparison' page</t>
-  </si>
-  <si>
     <t>TC_PC_020</t>
   </si>
   <si>
-    <t>Validate adding the Products to cart from the 'Product Comparison' page</t>
-  </si>
-  <si>
     <t>TC_PC_021</t>
   </si>
   <si>
-    <t>Validate removing the Products from the 'Product Comparison' page</t>
-  </si>
-  <si>
     <t>TC_PC_022</t>
   </si>
   <si>
@@ -921,12 +822,6 @@
     <t>TC_PC_024</t>
   </si>
   <si>
-    <t>Validate the 'Product Comparison' functionality in all the supported environments</t>
-  </si>
-  <si>
-    <t>TS_007</t>
-  </si>
-  <si>
     <t>Validate the Product Display Page functionality</t>
   </si>
   <si>
@@ -1062,9 +957,6 @@
     <t>TC_PDP_022</t>
   </si>
   <si>
-    <t>Validate 'Related Products' section in Product Display page</t>
-  </si>
-  <si>
     <t>TC_PDP_023</t>
   </si>
   <si>
@@ -1116,9 +1008,6 @@
     <t>TC_PDP_031</t>
   </si>
   <si>
-    <t>Validate the Reward Points displayed in the Product Display page</t>
-  </si>
-  <si>
     <t>TC_PDP_032</t>
   </si>
   <si>
@@ -1152,12 +1041,6 @@
     <t>TC_PDP_037</t>
   </si>
   <si>
-    <t>Validate the 'Product Display' page functionality in all the supported environments</t>
-  </si>
-  <si>
-    <t>TS_008</t>
-  </si>
-  <si>
     <t>Validate the working of 'Add to Cart' functionality</t>
   </si>
   <si>
@@ -1176,27 +1059,15 @@
     <t>TC_ATC_003</t>
   </si>
   <si>
-    <t>Validate adding the product to Cart from Search Results Page</t>
-  </si>
-  <si>
     <t>TC_ATC_004</t>
   </si>
   <si>
-    <t>Validate adding the product to Cart from the Related Products section of the Product Display Page</t>
-  </si>
-  <si>
     <t>TC_ATC_005</t>
   </si>
   <si>
-    <t>Validate adding the product to Cart from the Products displayed in the category or sub-category page</t>
-  </si>
-  <si>
     <t>TC_ATC_006</t>
   </si>
   <si>
-    <t>Validate adding the product to Cart from the Products displayed in the 'Featured' section of Home page</t>
-  </si>
-  <si>
     <t>TC_ATC_007</t>
   </si>
   <si>
@@ -1212,7 +1083,136 @@
     <t>TC_ATC_009</t>
   </si>
   <si>
-    <t>Validate the 'Add to Cart' page functionality in all the supported environments</t>
+    <t>RequiremenREQ_F Traceability Matrix (RTM) — OpenCart (Frontend)  |  https://demo.opencart.com  |  By: Rushikesh Bhadange</t>
+  </si>
+  <si>
+    <t>REQ_F_001</t>
+  </si>
+  <si>
+    <t>Validate whether the fields in the Register Account page are according the Client requiremenREQ_F (Examples- Height, Width, Number of characters etc.)</t>
+  </si>
+  <si>
+    <t>Validate the Password text entered into the 'Password' and 'Password Confirm' field of 'Register Account' functionality is toggled to hide iREQ_F visibility</t>
+  </si>
+  <si>
+    <t>Validate 'Register Account' functionality in all the supported environmenREQ_F</t>
+  </si>
+  <si>
+    <t>REQ_F_002</t>
+  </si>
+  <si>
+    <t>Validate the text into the Password field is toggled to hide iREQ_F visibility</t>
+  </si>
+  <si>
+    <t>Validate the Login page functionality in all the supported environmenREQ_F</t>
+  </si>
+  <si>
+    <t>REQ_F_003</t>
+  </si>
+  <si>
+    <t>Validate the Logout functionality in all the supported environmenREQ_F</t>
+  </si>
+  <si>
+    <t>REQ_F_004</t>
+  </si>
+  <si>
+    <t>Validate the Password entered into the 'Password' and 'Confirm' fields of 'Reset your Password' page is toggled to hide iREQ_F visibility</t>
+  </si>
+  <si>
+    <t>Validate the Password Reset functionality in all the supported environmenREQ_F</t>
+  </si>
+  <si>
+    <t>REQ_F_005</t>
+  </si>
+  <si>
+    <t>Validate searching by providing a search criteria which resulREQ_F in mulitple producREQ_F</t>
+  </si>
+  <si>
+    <t>Validate List and Grid views when only one Product is displayed in the search resulREQ_F</t>
+  </si>
+  <si>
+    <t>Validate List and Grid views when  multiple ProducREQ_F are displayed in the search resulREQ_F</t>
+  </si>
+  <si>
+    <t>Validate navigating to Product Compare Page from Search ResulREQ_F page</t>
+  </si>
+  <si>
+    <t>Validate User is able to sort the ProducREQ_F displayed in the Search ResulREQ_F</t>
+  </si>
+  <si>
+    <t>Validate the User can select how many produREQ_F can be displayed in the Search ResulREQ_F</t>
+  </si>
+  <si>
+    <t>Validate the Search functionality in all the supported environmenREQ_F</t>
+  </si>
+  <si>
+    <t>REQ_F_006</t>
+  </si>
+  <si>
+    <t>Validate adding the product for comparision from List View of Search ResulREQ_F page</t>
+  </si>
+  <si>
+    <t>Validate adding the product for comparision from Grid View of Search ResulREQ_F page</t>
+  </si>
+  <si>
+    <t>Validate navigating to 'Product Compare' page from Search resulREQ_F page</t>
+  </si>
+  <si>
+    <t>Validate 'Product Compare' page when no producREQ_F are added for comparison</t>
+  </si>
+  <si>
+    <t>Validate the success message which will be displayed after adding the ProducREQ_F for Comparison</t>
+  </si>
+  <si>
+    <t>Validate the 'Product Comparison' page when only two producREQ_F are added to the page for comparison</t>
+  </si>
+  <si>
+    <t>Validate the 'Product Comparison' page when three producREQ_F are added to the page for comparison</t>
+  </si>
+  <si>
+    <t>Validate the 'Product Comparison' page when four producREQ_F are added to the page for comparison</t>
+  </si>
+  <si>
+    <t>Validate that more than 4 producREQ_F cannot be added to the 'Product Comparison' page</t>
+  </si>
+  <si>
+    <t>Validate adding the ProducREQ_F to cart from the 'Product Comparison' page</t>
+  </si>
+  <si>
+    <t>Validate removing the ProducREQ_F from the 'Product Comparison' page</t>
+  </si>
+  <si>
+    <t>Validate the 'Product Comparison' functionality in all the supported environmenREQ_F</t>
+  </si>
+  <si>
+    <t>REQ_F_007</t>
+  </si>
+  <si>
+    <t>Validate 'Related ProducREQ_F' section in Product Display page</t>
+  </si>
+  <si>
+    <t>Validate the Reward PoinREQ_F displayed in the Product Display page</t>
+  </si>
+  <si>
+    <t>Validate the 'Product Display' page functionality in all the supported environmenREQ_F</t>
+  </si>
+  <si>
+    <t>REQ_F_008</t>
+  </si>
+  <si>
+    <t>Validate adding the product to Cart from Search ResulREQ_F Page</t>
+  </si>
+  <si>
+    <t>Validate adding the product to Cart from the Related ProducREQ_F section of the Product Display Page</t>
+  </si>
+  <si>
+    <t>Validate adding the product to Cart from the ProducREQ_F displayed in the category or sub-category page</t>
+  </si>
+  <si>
+    <t>Validate adding the product to Cart from the ProducREQ_F displayed in the 'Featured' section of Home page</t>
+  </si>
+  <si>
+    <t>Validate the 'Add to Cart' page functionality in all the supported environmenREQ_F</t>
   </si>
 </sst>
 </file>
@@ -1340,10 +1340,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1356,6 +1352,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1661,3602 +1661,3602 @@
   <dimension ref="A1:F180"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
     <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="57.453125" style="16" customWidth="1"/>
+    <col min="4" max="4" width="57.453125" style="14" customWidth="1"/>
     <col min="5" max="5" width="8.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="A1" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>10</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="F4" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>22</v>
+        <v>19</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>20</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>22</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>37</v>
+        <v>34</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>44</v>
+        <v>41</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>52</v>
+        <v>49</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>355</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>54</v>
+        <v>50</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>57</v>
+        <v>53</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>59</v>
+        <v>55</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>61</v>
+        <v>57</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>356</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>63</v>
+        <v>58</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>65</v>
+        <v>60</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>67</v>
+        <v>62</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>69</v>
+        <v>64</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>71</v>
+        <v>66</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>357</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>75</v>
+        <v>68</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>77</v>
+        <v>70</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="D32" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>79</v>
-      </c>
       <c r="E32" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>81</v>
+        <v>74</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>83</v>
+        <v>76</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>85</v>
+        <v>78</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>79</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>87</v>
+        <v>80</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>89</v>
+        <v>82</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>91</v>
+        <v>84</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>94</v>
+        <v>87</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>88</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>97</v>
+        <v>90</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>91</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>100</v>
+        <v>93</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>102</v>
+        <v>95</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>359</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>104</v>
+        <v>96</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>97</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>106</v>
+        <v>98</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>109</v>
+        <v>101</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>102</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>111</v>
+        <v>103</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>104</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>113</v>
+        <v>105</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>116</v>
+        <v>108</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>118</v>
+        <v>110</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>120</v>
+        <v>112</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>113</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>122</v>
+        <v>114</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>124</v>
+        <v>116</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>360</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>125</v>
+        <v>361</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>128</v>
+        <v>118</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>125</v>
+        <v>361</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>130</v>
+        <v>120</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>121</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>125</v>
+        <v>361</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>123</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D56" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="B56" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>134</v>
-      </c>
       <c r="E56" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>125</v>
+        <v>361</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>136</v>
+      <c r="D57" s="11" t="s">
+        <v>127</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>125</v>
+        <v>361</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>138</v>
+        <v>128</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>129</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
-        <v>125</v>
+        <v>361</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>140</v>
+        <v>130</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>125</v>
+        <v>361</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>143</v>
+        <v>133</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>134</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>125</v>
+        <v>361</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>145</v>
+        <v>135</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>136</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>125</v>
+        <v>361</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>147</v>
+        <v>137</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>138</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>125</v>
+        <v>361</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>149</v>
+        <v>139</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>362</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="8" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="D64" s="15" t="s">
-        <v>153</v>
+        <v>141</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>142</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="8" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>155</v>
+        <v>143</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>144</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" s="8" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="D66" s="15" t="s">
-        <v>157</v>
+        <v>145</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>146</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A67" s="8" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>159</v>
+        <v>147</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>148</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D68" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D68" s="13" t="s">
-        <v>161</v>
-      </c>
       <c r="E68" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A69" s="8" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B69" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C69" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C69" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>163</v>
+      <c r="D69" s="13" t="s">
+        <v>152</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A70" s="8" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="D70" s="15" t="s">
-        <v>165</v>
+        <v>153</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>154</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" s="8" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="D71" s="15" t="s">
-        <v>167</v>
+        <v>155</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>156</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" s="8" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="D72" s="15" t="s">
-        <v>169</v>
+        <v>157</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>158</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="8" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D73" s="15" t="s">
-        <v>171</v>
+        <v>159</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>160</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" s="8" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="D74" s="15" t="s">
-        <v>173</v>
+        <v>161</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>162</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="8" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="D75" s="15" t="s">
-        <v>175</v>
+        <v>163</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>164</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="8" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="D76" s="15" t="s">
-        <v>177</v>
+        <v>165</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>166</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="8" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="D77" s="15" t="s">
-        <v>179</v>
+        <v>167</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>168</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>181</v>
+        <v>169</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>170</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>183</v>
+        <v>171</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>185</v>
+        <v>173</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>174</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D81" s="13" t="s">
-        <v>187</v>
+        <v>175</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>176</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D82" s="13" t="s">
-        <v>189</v>
+        <v>177</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D83" s="13" t="s">
-        <v>191</v>
+        <v>179</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>180</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="D84" s="13" t="s">
-        <v>193</v>
+        <v>181</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>182</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D85" s="14" t="s">
-        <v>195</v>
+        <v>183</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>184</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D86" s="13" t="s">
-        <v>198</v>
+        <v>186</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>187</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A87" s="8" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="D87" s="15" t="s">
-        <v>200</v>
+        <v>188</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>364</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="8" t="s">
-        <v>150</v>
+        <v>363</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="D88" s="15" t="s">
-        <v>202</v>
+        <v>189</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>365</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="D89" s="13" t="s">
-        <v>206</v>
+        <v>191</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>192</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D90" s="13" t="s">
-        <v>208</v>
+        <v>193</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>194</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D91" s="13" t="s">
-        <v>210</v>
+        <v>195</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>196</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="D92" s="13" t="s">
-        <v>212</v>
+        <v>197</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="D93" s="13" t="s">
-        <v>214</v>
+        <v>199</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>367</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>216</v>
+        <v>200</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>201</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D95" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D95" s="13" t="s">
-        <v>218</v>
-      </c>
       <c r="E95" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C96" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="D96" s="13" t="s">
-        <v>220</v>
+      <c r="D96" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D97" s="13" t="s">
-        <v>222</v>
+        <v>206</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>207</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="D98" s="13" t="s">
-        <v>224</v>
+        <v>208</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>209</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D99" s="13" t="s">
-        <v>226</v>
+        <v>210</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>368</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="D100" s="13" t="s">
-        <v>228</v>
+        <v>211</v>
+      </c>
+      <c r="D100" s="11" t="s">
+        <v>369</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="D101" s="13" t="s">
-        <v>230</v>
+        <v>212</v>
+      </c>
+      <c r="D101" s="11" t="s">
+        <v>370</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="D102" s="13" t="s">
-        <v>232</v>
+        <v>213</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>371</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="D103" s="13" t="s">
-        <v>234</v>
+        <v>214</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>372</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="D104" s="13" t="s">
-        <v>236</v>
+        <v>215</v>
+      </c>
+      <c r="D104" s="11" t="s">
+        <v>216</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>238</v>
+        <v>217</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>218</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="D106" s="13" t="s">
-        <v>240</v>
+        <v>219</v>
+      </c>
+      <c r="D106" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D107" s="14" t="s">
-        <v>242</v>
+        <v>221</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D108" s="13" t="s">
-        <v>245</v>
+        <v>224</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>225</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>247</v>
+        <v>226</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>227</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="D110" s="13" t="s">
-        <v>249</v>
+        <v>228</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>373</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="D111" s="13" t="s">
-        <v>253</v>
+        <v>230</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>231</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="D112" s="13" t="s">
-        <v>255</v>
+        <v>232</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>375</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="D113" s="13" t="s">
-        <v>257</v>
+        <v>233</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>376</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="D114" s="13" t="s">
-        <v>259</v>
+        <v>234</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>235</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>261</v>
+        <v>236</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>237</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D116" s="13" t="s">
-        <v>263</v>
+        <v>238</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>239</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="D117" s="13" t="s">
-        <v>265</v>
+        <v>240</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="D118" s="13" t="s">
-        <v>267</v>
+        <v>242</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>377</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D119" s="13" t="s">
-        <v>269</v>
+        <v>243</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>244</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="D120" s="13" t="s">
-        <v>271</v>
+        <v>245</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>378</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D121" s="13" t="s">
-        <v>273</v>
+        <v>246</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>247</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="D122" s="13" t="s">
-        <v>275</v>
+        <v>248</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>249</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C123" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="B123" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="D123" s="13" t="s">
-        <v>277</v>
+      <c r="D123" s="11" t="s">
+        <v>379</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B124" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C124" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C124" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="D124" s="13" t="s">
-        <v>279</v>
+      <c r="D124" s="11" t="s">
+        <v>252</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="D125" s="13" t="s">
-        <v>281</v>
+        <v>253</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>380</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="D126" s="13" t="s">
-        <v>283</v>
+        <v>254</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>255</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="D127" s="13" t="s">
-        <v>285</v>
+        <v>256</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>381</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="D128" s="13" t="s">
-        <v>287</v>
+        <v>257</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>382</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="D129" s="13" t="s">
-        <v>289</v>
+        <v>258</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>383</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="D130" s="13" t="s">
-        <v>291</v>
+        <v>259</v>
+      </c>
+      <c r="D130" s="11" t="s">
+        <v>384</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="D131" s="13" t="s">
-        <v>293</v>
+        <v>260</v>
+      </c>
+      <c r="D131" s="11" t="s">
+        <v>385</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="D132" s="13" t="s">
-        <v>295</v>
+        <v>261</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>262</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="D133" s="13" t="s">
-        <v>297</v>
+        <v>263</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>264</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="D134" s="13" t="s">
-        <v>299</v>
+        <v>265</v>
+      </c>
+      <c r="D134" s="11" t="s">
+        <v>386</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="D135" s="13" t="s">
-        <v>303</v>
+        <v>267</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>268</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="D136" s="13" t="s">
-        <v>305</v>
+        <v>269</v>
+      </c>
+      <c r="D136" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="D137" s="13" t="s">
-        <v>307</v>
+        <v>271</v>
+      </c>
+      <c r="D137" s="11" t="s">
+        <v>272</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="D138" s="13" t="s">
-        <v>309</v>
+        <v>273</v>
+      </c>
+      <c r="D138" s="11" t="s">
+        <v>274</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="D139" s="13" t="s">
-        <v>311</v>
+        <v>275</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>276</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D140" s="14" t="s">
-        <v>313</v>
+        <v>277</v>
+      </c>
+      <c r="D140" s="12" t="s">
+        <v>278</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="D141" s="13" t="s">
-        <v>316</v>
+        <v>280</v>
+      </c>
+      <c r="D141" s="11" t="s">
+        <v>281</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="D142" s="13" t="s">
-        <v>318</v>
+        <v>282</v>
+      </c>
+      <c r="D142" s="11" t="s">
+        <v>283</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D143" s="13" t="s">
-        <v>320</v>
+        <v>284</v>
+      </c>
+      <c r="D143" s="11" t="s">
+        <v>285</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="D144" s="13" t="s">
-        <v>322</v>
+        <v>286</v>
+      </c>
+      <c r="D144" s="11" t="s">
+        <v>287</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="D145" s="13" t="s">
-        <v>324</v>
+        <v>288</v>
+      </c>
+      <c r="D145" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="D146" s="13" t="s">
-        <v>326</v>
+        <v>290</v>
+      </c>
+      <c r="D146" s="11" t="s">
+        <v>291</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="D147" s="13" t="s">
-        <v>328</v>
+        <v>292</v>
+      </c>
+      <c r="D147" s="11" t="s">
+        <v>293</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="D148" s="13" t="s">
-        <v>330</v>
+        <v>294</v>
+      </c>
+      <c r="D148" s="11" t="s">
+        <v>295</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="D149" s="13" t="s">
-        <v>332</v>
+        <v>296</v>
+      </c>
+      <c r="D149" s="11" t="s">
+        <v>297</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="D150" s="13" t="s">
-        <v>334</v>
+        <v>298</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>299</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C151" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="D151" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="C151" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="D151" s="13" t="s">
-        <v>336</v>
-      </c>
       <c r="E151" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="D152" s="13" t="s">
-        <v>338</v>
+        <v>302</v>
+      </c>
+      <c r="D152" s="11" t="s">
+        <v>303</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="D153" s="13" t="s">
-        <v>340</v>
+        <v>304</v>
+      </c>
+      <c r="D153" s="11" t="s">
+        <v>305</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="D154" s="13" t="s">
-        <v>342</v>
+        <v>306</v>
+      </c>
+      <c r="D154" s="11" t="s">
+        <v>307</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="D155" s="13" t="s">
-        <v>344</v>
+        <v>308</v>
+      </c>
+      <c r="D155" s="11" t="s">
+        <v>309</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="D156" s="13" t="s">
-        <v>346</v>
+        <v>310</v>
+      </c>
+      <c r="D156" s="11" t="s">
+        <v>388</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="D157" s="13" t="s">
-        <v>348</v>
+        <v>311</v>
+      </c>
+      <c r="D157" s="11" t="s">
+        <v>312</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="D158" s="13" t="s">
-        <v>350</v>
+        <v>313</v>
+      </c>
+      <c r="D158" s="11" t="s">
+        <v>314</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="D159" s="13" t="s">
-        <v>352</v>
+        <v>315</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>316</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="D160" s="13" t="s">
-        <v>354</v>
+        <v>317</v>
+      </c>
+      <c r="D160" s="11" t="s">
+        <v>318</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="D161" s="13" t="s">
-        <v>356</v>
+        <v>319</v>
+      </c>
+      <c r="D161" s="11" t="s">
+        <v>320</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="D162" s="13" t="s">
-        <v>358</v>
+        <v>321</v>
+      </c>
+      <c r="D162" s="11" t="s">
+        <v>322</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="D163" s="13" t="s">
-        <v>360</v>
+        <v>323</v>
+      </c>
+      <c r="D163" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="D164" s="13" t="s">
-        <v>362</v>
+        <v>325</v>
+      </c>
+      <c r="D164" s="11" t="s">
+        <v>326</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="D165" s="13" t="s">
-        <v>364</v>
+        <v>327</v>
+      </c>
+      <c r="D165" s="11" t="s">
+        <v>389</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="D166" s="13" t="s">
-        <v>366</v>
+        <v>328</v>
+      </c>
+      <c r="D166" s="11" t="s">
+        <v>329</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="D167" s="13" t="s">
-        <v>368</v>
+        <v>330</v>
+      </c>
+      <c r="D167" s="11" t="s">
+        <v>331</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="D168" s="13" t="s">
-        <v>370</v>
+        <v>332</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>333</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="D169" s="13" t="s">
-        <v>372</v>
+        <v>334</v>
+      </c>
+      <c r="D169" s="11" t="s">
+        <v>335</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="D170" s="13" t="s">
-        <v>374</v>
+        <v>336</v>
+      </c>
+      <c r="D170" s="11" t="s">
+        <v>337</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
-        <v>300</v>
+        <v>387</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="D171" s="13" t="s">
-        <v>376</v>
+        <v>338</v>
+      </c>
+      <c r="D171" s="11" t="s">
+        <v>390</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="D172" s="13" t="s">
-        <v>380</v>
+        <v>340</v>
+      </c>
+      <c r="D172" s="11" t="s">
+        <v>341</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="D173" s="13" t="s">
-        <v>382</v>
+        <v>342</v>
+      </c>
+      <c r="D173" s="11" t="s">
+        <v>343</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="D174" s="13" t="s">
-        <v>384</v>
+        <v>344</v>
+      </c>
+      <c r="D174" s="11" t="s">
+        <v>392</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="D175" s="13" t="s">
-        <v>386</v>
+        <v>345</v>
+      </c>
+      <c r="D175" s="11" t="s">
+        <v>393</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="D176" s="13" t="s">
-        <v>388</v>
+        <v>346</v>
+      </c>
+      <c r="D176" s="11" t="s">
+        <v>394</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="D177" s="13" t="s">
-        <v>390</v>
+        <v>347</v>
+      </c>
+      <c r="D177" s="11" t="s">
+        <v>395</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="D178" s="13" t="s">
-        <v>392</v>
+        <v>348</v>
+      </c>
+      <c r="D178" s="11" t="s">
+        <v>349</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="D179" s="13" t="s">
-        <v>394</v>
+        <v>350</v>
+      </c>
+      <c r="D179" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="D180" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="D180" s="11" t="s">
         <v>396</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
